--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1103,23 +1103,7 @@
     <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime
-Micro.AntibioticSensitivityComment.SpecimenTakenDateTime
-Micro.BacteriologyReports.SpecimenTakenDateTime
-Micro.MicroAntibioticLevel.SpecimenTakenDateTime
-Micro.MicroAudit.SpecimenTakenDateTime
-Micro.Microbiology.SpecimenTakenDateTime
-Micro.MicroOrderedTest.SpecimenTakenDateTime
-Micro.MicroSterilityResults.SpecimenTakenDateTime
-Micro.MycobacteriologyReports.SpecimenTakenDateTime
-Micro.Mycology.SpecimenTakenDateTime
-Micro.MycologyReports.SpecimenTakenDateTime
-Micro.Parasitology.SpecimenTakenDateTime
-Micro.ParasitologyReports.SpecimenTakenDateTime
-Micro.ParasitologyStage.SpecimenTakenDateTime
-SStaff.SMicroOrderedTest.SpecimenTakenDateTime
-Micro.Virology.SpecimenTakenDateTime
-Micro.VirologyReports.SpecimenTakenDateTime</t>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -2108,7 +2092,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="238.10546875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="57.953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -662,13 +662,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -925,13 +925,13 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1122,6 +1122,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.ReportCompletedDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1129,12 +1135,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1153,6 +1153,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1163,9 +1166,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1289,16 +1289,16 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.SpecimenComment</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.SpecimenComment</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -1378,6 +1378,12 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
     <t>&lt; 123038009 |Specimen|</t>
   </si>
   <si>
@@ -1388,12 +1394,6 @@
   </si>
   <si>
     <t>704319004 |Inherent in|</t>
-  </si>
-  <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -2085,14 +2085,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="238.10546875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="238.10546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2331,22 +2331,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2968,13 +2968,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3094,13 +3094,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3220,13 +3220,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3348,13 +3348,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3465,25 +3465,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3598,13 +3598,13 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3724,13 +3724,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3849,16 +3849,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -3977,16 +3977,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4105,16 +4105,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4225,25 +4225,25 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4355,16 +4355,16 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4481,16 +4481,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4601,22 +4601,22 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4727,22 +4727,22 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4853,25 +4853,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4988,16 +4988,16 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5118,16 +5118,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5237,28 +5237,28 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5370,13 +5370,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5496,13 +5496,13 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5615,25 +5615,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP28" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5749,16 +5749,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5871,25 +5871,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6003,19 +6003,19 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6125,25 +6125,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6251,25 +6251,25 @@
         <v>338</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6381,28 +6381,28 @@
         <v>338</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AR34" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6507,28 +6507,28 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>355</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6642,13 +6642,13 @@
         <v>364</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>367</v>
@@ -6764,25 +6764,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6893,16 +6893,16 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7018,25 +7018,25 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -7143,28 +7143,28 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7272,25 +7272,25 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7403,16 +7403,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7523,25 +7523,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>436</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>437</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>440</v>
@@ -7652,25 +7652,25 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7783,16 +7783,16 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7910,13 +7910,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8036,13 +8036,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8164,13 +8164,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8285,16 +8285,16 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8409,16 +8409,16 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8534,19 +8534,19 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8662,19 +8662,19 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8794,13 +8794,13 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8915,16 +8915,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9041,16 +9041,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9167,16 +9167,16 @@
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9295,16 +9295,16 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9422,13 +9422,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9548,13 +9548,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9676,13 +9676,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9798,22 +9798,22 @@
         <v>84</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AO61" t="s" s="2">
+      <c r="AQ61" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -9926,25 +9926,25 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10057,16 +10057,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10182,25 +10182,25 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -10313,16 +10313,16 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -822,28 +822,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -854,6 +832,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -975,6 +978,12 @@
   </si>
   <si>
     <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -4927,7 +4936,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4945,16 +4954,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4979,7 +4988,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -4994,10 +5003,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5005,13 +5014,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5055,7 +5064,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5073,10 +5082,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5124,10 +5133,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5135,14 +5144,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5164,16 +5173,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5201,10 +5210,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5222,7 +5231,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5243,30 +5252,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5387,10 +5396,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5513,10 +5522,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5539,19 +5548,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5600,7 +5609,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5615,7 +5624,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5627,10 +5636,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5641,10 +5650,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5670,16 +5679,16 @@
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5728,7 +5737,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5755,10 +5764,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5769,10 +5778,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5795,19 +5804,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5856,7 +5865,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5871,25 +5880,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5897,10 +5906,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5923,16 +5932,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5982,7 +5991,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6009,13 +6018,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6023,14 +6032,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6049,19 +6058,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6110,7 +6119,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6131,19 +6140,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6151,14 +6160,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6177,19 +6186,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6226,7 +6235,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6236,7 +6245,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6245,10 +6254,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6257,19 +6266,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6277,16 +6286,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6305,19 +6314,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6366,7 +6375,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6375,31 +6384,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6407,10 +6416,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6433,16 +6442,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6492,7 +6501,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6507,10 +6516,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6519,13 +6528,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6533,10 +6542,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6559,17 +6568,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6618,7 +6627,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6633,25 +6642,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6659,10 +6668,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6685,19 +6694,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6746,7 +6755,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6755,10 +6764,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6770,27 +6779,27 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6816,16 +6825,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6854,7 +6863,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6872,7 +6881,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6881,7 +6890,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6902,7 +6911,7 @@
         <v>137</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6913,14 +6922,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6942,16 +6951,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6979,10 +6988,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7000,7 +7009,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7024,27 +7033,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7067,19 +7076,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7128,7 +7137,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7143,10 +7152,10 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>84</v>
@@ -7155,10 +7164,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7169,10 +7178,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7198,13 +7207,13 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7230,13 +7239,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7254,7 +7263,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7278,27 +7287,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7324,16 +7333,16 @@
         <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7358,13 +7367,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7382,7 +7391,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7409,10 +7418,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7423,10 +7432,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7449,16 +7458,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7508,7 +7517,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7523,36 +7532,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7575,16 +7584,16 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7634,7 +7643,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7658,27 +7667,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7701,19 +7710,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7762,7 +7771,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7783,7 @@
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7789,10 +7798,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7803,10 +7812,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7927,10 +7936,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8053,14 +8062,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8082,10 +8091,10 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -8140,7 +8149,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8181,10 +8190,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8207,13 +8216,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8264,7 +8273,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8273,7 +8282,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8291,10 +8300,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8305,10 +8314,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8331,13 +8340,13 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8388,7 +8397,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8397,7 +8406,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8415,10 +8424,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8429,10 +8438,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8458,16 +8467,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8495,10 +8504,10 @@
         <v>118</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8516,7 +8525,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8540,13 +8549,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8557,10 +8566,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8586,16 +8595,16 @@
         <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8620,13 +8629,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8644,7 +8653,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8668,13 +8677,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8685,10 +8694,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8711,17 +8720,17 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8770,7 +8779,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8800,7 +8809,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8811,10 +8820,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8840,10 +8849,10 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8894,7 +8903,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8921,10 +8930,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8935,10 +8944,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8961,16 +8970,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9020,7 +9029,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9047,10 +9056,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9061,10 +9070,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9087,16 +9096,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9146,7 +9155,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9173,10 +9182,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9187,10 +9196,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9213,19 +9222,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9274,7 +9283,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9301,10 +9310,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9315,10 +9324,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9439,10 +9448,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9565,14 +9574,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9594,10 +9603,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -9652,7 +9661,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9693,10 +9702,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9722,16 +9731,16 @@
         <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9756,13 +9765,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9780,7 +9789,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>94</v>
@@ -9804,16 +9813,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -9821,10 +9830,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9847,19 +9856,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9908,7 +9917,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9932,27 +9941,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9978,16 +9987,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10015,10 +10024,10 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10036,7 +10045,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10045,7 +10054,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10066,7 +10075,7 @@
         <v>137</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10077,14 +10086,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10106,16 +10115,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10143,10 +10152,10 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10164,7 +10173,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10188,27 +10197,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10234,16 +10243,16 @@
         <v>85</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10292,7 +10301,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10319,10 +10328,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -928,7 +928,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -980,7 +980,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1109,7 +1109,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
@@ -1131,7 +1131,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1162,7 +1162,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1298,7 +1298,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1387,7 +1387,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -2094,7 +2094,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="238.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="234.23828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -983,7 +983,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1112,7 +1112,7 @@
     <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1163,6 +1163,9 @@
   </si>
   <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -6645,22 +6648,22 @@
         <v>366</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6668,10 +6671,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6694,19 +6697,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6755,7 +6758,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6764,10 +6767,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6779,27 +6782,27 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6825,16 +6828,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6863,7 +6866,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6881,7 +6884,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6890,7 +6893,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6911,7 +6914,7 @@
         <v>137</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6922,14 +6925,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6951,16 +6954,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6988,10 +6991,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7009,7 +7012,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7033,27 +7036,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7076,19 +7079,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7137,7 +7140,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7152,10 +7155,10 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>84</v>
@@ -7164,10 +7167,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7178,10 +7181,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7207,13 +7210,13 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7239,13 +7242,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7263,7 +7266,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7287,27 +7290,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7333,16 +7336,16 @@
         <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7367,13 +7370,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7391,7 +7394,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7418,10 +7421,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7432,10 +7435,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7458,16 +7461,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7517,7 +7520,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7532,36 +7535,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7584,16 +7587,16 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7643,7 +7646,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7667,27 +7670,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7710,19 +7713,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7771,7 +7774,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7783,7 +7786,7 @@
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7798,10 +7801,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7812,10 +7815,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7936,10 +7939,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8062,14 +8065,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8091,10 +8094,10 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -8149,7 +8152,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8190,10 +8193,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8216,13 +8219,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8273,7 +8276,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8282,7 +8285,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8300,10 +8303,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8314,10 +8317,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8340,13 +8343,13 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8397,7 +8400,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8406,7 +8409,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8424,10 +8427,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8438,10 +8441,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8467,16 +8470,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8504,10 +8507,10 @@
         <v>118</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8525,7 +8528,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8549,13 +8552,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8566,10 +8569,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8595,16 +8598,16 @@
         <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8629,13 +8632,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8653,7 +8656,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8677,13 +8680,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8694,10 +8697,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8720,17 +8723,17 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8779,7 +8782,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8809,7 +8812,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8820,10 +8823,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8849,10 +8852,10 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8903,7 +8906,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8930,10 +8933,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8944,10 +8947,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8970,16 +8973,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9029,7 +9032,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9056,10 +9059,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9070,10 +9073,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9096,16 +9099,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9155,7 +9158,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9182,10 +9185,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9196,10 +9199,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9222,19 +9225,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9283,7 +9286,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9310,10 +9313,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9324,10 +9327,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9448,10 +9451,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9574,14 +9577,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9603,10 +9606,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -9661,7 +9664,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9702,10 +9705,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9731,13 +9734,13 @@
         <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>274</v>
@@ -9765,10 +9768,10 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>276</v>
@@ -9789,7 +9792,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>94</v>
@@ -9813,7 +9816,7 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>279</v>
@@ -9830,10 +9833,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9856,19 +9859,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9917,7 +9920,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9941,27 +9944,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9987,16 +9990,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10024,10 +10027,10 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10045,7 +10048,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10054,7 +10057,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10075,7 +10078,7 @@
         <v>137</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10086,14 +10089,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10115,16 +10118,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10152,10 +10155,10 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10173,7 +10176,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10197,27 +10200,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10243,16 +10246,16 @@
         <v>85</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10301,7 +10304,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10328,10 +10331,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -935,6 +941,136 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -2059,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR65"/>
+  <dimension ref="A1:AR72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -2097,7 +2233,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="234.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -4026,7 +4162,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4057,10 +4193,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4096,7 +4232,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4111,7 +4247,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4123,10 +4259,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4137,10 +4273,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4166,13 +4302,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4186,7 +4322,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4222,7 +4358,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4237,7 +4373,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4249,10 +4385,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4263,10 +4399,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4289,13 +4425,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4346,7 +4482,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4373,10 +4509,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4387,10 +4523,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4413,16 +4549,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4472,7 +4608,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4499,10 +4635,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4513,14 +4649,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4539,17 +4675,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4598,7 +4734,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4619,16 +4755,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4639,14 +4775,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4665,16 +4801,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4724,7 +4860,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4745,16 +4881,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4765,10 +4901,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4794,16 +4930,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4832,7 +4968,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4850,7 +4986,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4871,19 +5007,19 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4891,10 +5027,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4920,16 +5056,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4939,7 +5075,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4957,16 +5093,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4976,7 +5112,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4991,7 +5127,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5006,10 +5142,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5017,13 +5153,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5048,16 +5184,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5067,7 +5203,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5085,10 +5221,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5106,7 +5242,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5136,10 +5272,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5147,14 +5283,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5176,16 +5312,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5213,10 +5349,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5234,7 +5370,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5255,30 +5391,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5399,10 +5535,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5525,10 +5661,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5551,19 +5687,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5612,7 +5748,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5627,7 +5763,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5639,10 +5775,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5653,10 +5789,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5676,23 +5812,19 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5740,7 +5872,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5752,7 +5884,7 @@
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5767,10 +5899,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>165</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5781,46 +5913,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>167</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5856,52 +5986,52 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5909,10 +6039,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5923,10 +6053,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -5935,18 +6065,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5994,13 +6126,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6009,7 +6141,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6021,13 +6153,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6035,14 +6167,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6061,20 +6193,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>323</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6122,7 +6252,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6143,19 +6273,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6163,14 +6293,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6189,19 +6319,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>334</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6238,17 +6366,19 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6257,31 +6387,31 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>341</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6289,16 +6419,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6317,19 +6445,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>348</v>
+        <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6378,7 +6504,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6387,31 +6513,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>341</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6419,10 +6545,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6436,7 +6562,7 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6445,18 +6571,20 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6504,7 +6632,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6519,10 +6647,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6531,13 +6659,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6545,10 +6673,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6559,10 +6687,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6571,17 +6699,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>362</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6630,13 +6760,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6645,25 +6775,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>367</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6671,10 +6801,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6682,7 +6812,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6697,19 +6827,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6758,7 +6888,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6767,42 +6897,42 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>379</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6813,32 +6943,30 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>361</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6862,11 +6990,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6884,16 +7014,16 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6911,13 +7041,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -6925,21 +7055,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6948,22 +7078,22 @@
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>183</v>
+        <v>368</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6988,13 +7118,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7012,13 +7142,13 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
@@ -7033,41 +7163,41 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>373</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>378</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>95</v>
@@ -7076,22 +7206,22 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7128,52 +7258,50 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>386</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>411</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7181,14 +7309,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>378</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7198,27 +7328,29 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>393</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
+        <v>381</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7242,13 +7374,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7266,7 +7398,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7275,42 +7407,42 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>386</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>395</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>424</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7324,29 +7456,27 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>397</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>426</v>
+        <v>398</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7370,13 +7500,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7394,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7409,10 +7539,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7421,13 +7551,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7435,10 +7565,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7449,7 +7579,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>95</v>
@@ -7458,21 +7588,21 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>435</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7520,13 +7650,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7535,36 +7665,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7578,27 +7708,29 @@
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7646,7 +7778,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7655,10 +7787,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>424</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7670,27 +7802,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7701,10 +7833,10 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -7713,19 +7845,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>455</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7750,13 +7882,11 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7774,19 +7904,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7801,10 +7931,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>461</v>
+        <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7815,21 +7945,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7841,16 +7971,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7874,13 +8008,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7898,19 +8032,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7922,31 +8056,31 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7956,7 +8090,7 @@
         <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -7965,18 +8099,20 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8024,7 +8160,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>449</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8036,13 +8172,13 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8051,10 +8187,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>165</v>
+        <v>458</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8065,46 +8201,44 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8128,13 +8262,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8152,43 +8286,43 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8219,16 +8353,20 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8252,13 +8390,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8285,7 +8423,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8303,10 +8441,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8317,10 +8455,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8334,7 +8472,7 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
@@ -8343,15 +8481,17 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8400,7 +8540,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8409,42 +8549,42 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>485</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>486</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8467,20 +8607,18 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>491</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8504,13 +8642,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8528,7 +8666,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8552,27 +8690,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>402</v>
+        <v>497</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8595,19 +8733,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8632,13 +8770,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8656,7 +8794,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8668,7 +8806,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>505</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8680,13 +8818,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8697,10 +8835,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8723,18 +8861,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>498</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>499</v>
+        <v>162</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>500</v>
+        <v>163</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>501</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8782,7 +8918,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>497</v>
+        <v>164</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8794,7 +8930,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8812,7 +8948,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>502</v>
+        <v>165</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8823,21 +8959,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8849,15 +8985,17 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>504</v>
+        <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8906,19 +9044,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>503</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -8933,10 +9071,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>506</v>
+        <v>165</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8947,14 +9085,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>511</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8967,24 +9105,26 @@
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>508</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9032,7 +9172,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9044,7 +9184,7 @@
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9059,10 +9199,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9073,10 +9213,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9087,7 +9227,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9096,20 +9236,18 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N56" t="s" s="2">
         <v>518</v>
       </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9158,16 +9296,16 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9185,10 +9323,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9199,10 +9337,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9213,7 +9351,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9222,23 +9360,19 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O57" t="s" s="2">
         <v>524</v>
       </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9286,16 +9420,16 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9313,10 +9447,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9327,10 +9461,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9353,16 +9487,20 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>162</v>
+        <v>527</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9386,13 +9524,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>531</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9410,7 +9548,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>164</v>
+        <v>526</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9422,7 +9560,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9434,13 +9572,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9451,14 +9589,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9477,18 +9615,20 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>141</v>
+        <v>536</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>537</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9512,13 +9652,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9536,7 +9676,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>171</v>
+        <v>535</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9548,7 +9688,7 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9560,13 +9700,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9577,45 +9717,43 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>543</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>467</v>
+        <v>544</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>149</v>
+        <v>546</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9664,19 +9802,19 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>469</v>
+        <v>542</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9694,7 +9832,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>137</v>
+        <v>547</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9705,10 +9843,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9716,7 +9854,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>94</v>
@@ -9728,23 +9866,19 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9768,13 +9902,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>534</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9792,10 +9926,10 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>94</v>
@@ -9816,16 +9950,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>535</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>279</v>
+        <v>520</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>280</v>
+        <v>551</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>281</v>
+        <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -9833,10 +9967,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9847,7 +9981,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -9859,20 +9993,18 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>373</v>
+        <v>553</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9920,13 +10052,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -9944,27 +10076,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>540</v>
+        <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>381</v>
+        <v>557</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>382</v>
+        <v>558</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9975,7 +10107,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -9984,23 +10116,21 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>183</v>
+        <v>560</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10024,13 +10154,13 @@
         <v>84</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10048,16 +10178,16 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>546</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10075,10 +10205,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>137</v>
+        <v>557</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>391</v>
+        <v>564</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10089,14 +10219,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10112,22 +10242,22 @@
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>394</v>
+        <v>566</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>395</v>
+        <v>567</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>396</v>
+        <v>568</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>397</v>
+        <v>569</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10152,13 +10282,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10176,7 +10306,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10200,27 +10330,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>401</v>
+        <v>570</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>402</v>
+        <v>571</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10231,7 +10361,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10243,20 +10373,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>549</v>
+        <v>162</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10304,47 +10430,941 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>548</v>
+        <v>164</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AI65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
+      <c r="H66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR65" t="s" s="2">
+      <c r="AK68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR65">
+  <autoFilter ref="A1:AR72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10354,7 +11374,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>1476-1: fixed value = http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
